--- a/core/tests/testcases/basics/03_4nurses_3shifts_7days_shift_type_requirement_shift_type_all.xlsx
+++ b/core/tests/testcases/basics/03_4nurses_3shifts_7days_shift_type_requirement_shift_type_all.xlsx
@@ -520,81 +520,11 @@
       <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -603,7 +533,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
